--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N80_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N80_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>97.71983067020722</v>
+        <v>15.87947248390867</v>
       </c>
       <c r="D2" t="n">
-        <v>96.05709110329759</v>
+        <v>15.60927730428586</v>
       </c>
       <c r="E2" t="n">
-        <v>22.31267078997743</v>
+        <v>3.625809003371332</v>
       </c>
       <c r="F2" t="n">
-        <v>21.64261319305134</v>
+        <v>3.516924643870843</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>54.14356711763212</v>
+        <v>8.79832965661522</v>
       </c>
       <c r="D3" t="n">
-        <v>52.56900385233573</v>
+        <v>8.542463126004558</v>
       </c>
       <c r="E3" t="n">
-        <v>22.31267078997743</v>
+        <v>3.625809003371332</v>
       </c>
       <c r="F3" t="n">
-        <v>21.64261319305134</v>
+        <v>3.516924643870843</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.91079359841661</v>
+        <v>5.185503959742698</v>
       </c>
       <c r="D4" t="n">
-        <v>30.51889431784018</v>
+        <v>4.95932032664903</v>
       </c>
       <c r="E4" t="n">
-        <v>22.31267078997743</v>
+        <v>3.625809003371332</v>
       </c>
       <c r="F4" t="n">
-        <v>21.64261319305134</v>
+        <v>3.516924643870843</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.70603240496768</v>
+        <v>8.564730265807249</v>
       </c>
       <c r="D5" t="n">
-        <v>48.97276769091821</v>
+        <v>7.95807474977421</v>
       </c>
       <c r="E5" t="n">
-        <v>22.31267078997743</v>
+        <v>3.625809003371332</v>
       </c>
       <c r="F5" t="n">
-        <v>21.64261319305134</v>
+        <v>3.516924643870843</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>42.37425607883465</v>
+        <v>6.885816612810631</v>
       </c>
       <c r="D6" t="n">
-        <v>43.0199335731574</v>
+        <v>6.990739205638078</v>
       </c>
       <c r="E6" t="n">
-        <v>22.31267078997743</v>
+        <v>3.625809003371332</v>
       </c>
       <c r="F6" t="n">
-        <v>21.64261319305134</v>
+        <v>3.516924643870843</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.76259553521163</v>
+        <v>8.57392177447189</v>
       </c>
       <c r="D7" t="n">
-        <v>47.85259516679876</v>
+        <v>7.776046714604798</v>
       </c>
       <c r="E7" t="n">
-        <v>22.31267078997743</v>
+        <v>3.625809003371332</v>
       </c>
       <c r="F7" t="n">
-        <v>21.64261319305134</v>
+        <v>3.516924643870843</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.05406364925624</v>
+        <v>2.608785343004139</v>
       </c>
       <c r="D8" t="n">
-        <v>16.42631655296606</v>
+        <v>2.669276439856985</v>
       </c>
       <c r="E8" t="n">
-        <v>22.31267078997743</v>
+        <v>3.625809003371332</v>
       </c>
       <c r="F8" t="n">
-        <v>21.64261319305134</v>
+        <v>3.516924643870843</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.17213463268802</v>
+        <v>6.040471877811804</v>
       </c>
       <c r="D9" t="n">
-        <v>37.85088190879915</v>
+        <v>6.150768310179862</v>
       </c>
       <c r="E9" t="n">
-        <v>22.31267078997743</v>
+        <v>3.625809003371332</v>
       </c>
       <c r="F9" t="n">
-        <v>21.64261319305134</v>
+        <v>3.516924643870843</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
